--- a/Fixture_10ma.xlsx
+++ b/Fixture_10ma.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\CopaApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77F1D9D1-1C09-4D72-B3BE-4F6DAB010408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0B6990-617C-47C6-A77B-526E60EBA844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="60">
   <si>
     <r>
       <rPr>
@@ -113,12 +113,108 @@
   <si>
     <t>GyT Celeste</t>
   </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>10:12</t>
+  </si>
+  <si>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>10:24</t>
+  </si>
+  <si>
+    <t>10:34</t>
+  </si>
+  <si>
+    <t>10:36</t>
+  </si>
+  <si>
+    <t>10:46</t>
+  </si>
+  <si>
+    <t>10:48</t>
+  </si>
+  <si>
+    <t>10:58</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>11:24</t>
+  </si>
+  <si>
+    <t>11:34</t>
+  </si>
+  <si>
+    <t>11:36</t>
+  </si>
+  <si>
+    <t>11:46</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>11:58</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>12:22</t>
+  </si>
+  <si>
+    <t>12:24</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>12:36</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>12:58</t>
+  </si>
+  <si>
+    <t>Hs Inicio</t>
+  </si>
+  <si>
+    <t>Hs Fin</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -144,8 +240,21 @@
       <name val="Palatino Linotype"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -157,8 +266,14 @@
         <fgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -181,11 +296,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -212,6 +353,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -517,16 +670,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="4"/>
     <col min="2" max="2" width="6.44140625" customWidth="1"/>
     <col min="3" max="4" width="39.33203125" customWidth="1"/>
     <col min="5" max="5" width="9.5546875" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
@@ -542,8 +697,14 @@
       <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F1" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>9</v>
       </c>
@@ -557,8 +718,14 @@
         <v>5</v>
       </c>
       <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>9</v>
       </c>
@@ -572,8 +739,14 @@
         <v>7</v>
       </c>
       <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>9</v>
       </c>
@@ -587,8 +760,14 @@
         <v>9</v>
       </c>
       <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>9</v>
       </c>
@@ -602,8 +781,14 @@
         <v>6</v>
       </c>
       <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>9</v>
       </c>
@@ -617,8 +802,14 @@
         <v>5</v>
       </c>
       <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>9</v>
       </c>
@@ -632,8 +823,14 @@
         <v>7</v>
       </c>
       <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>9</v>
       </c>
@@ -647,8 +844,14 @@
         <v>8</v>
       </c>
       <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>9</v>
       </c>
@@ -662,8 +865,14 @@
         <v>6</v>
       </c>
       <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F9" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -677,8 +886,14 @@
         <v>5</v>
       </c>
       <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -692,8 +907,14 @@
         <v>9</v>
       </c>
       <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -707,8 +928,14 @@
         <v>8</v>
       </c>
       <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -722,8 +949,14 @@
         <v>6</v>
       </c>
       <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>9</v>
       </c>
@@ -737,8 +970,14 @@
         <v>7</v>
       </c>
       <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>9</v>
       </c>
@@ -752,8 +991,14 @@
         <v>9</v>
       </c>
       <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>9</v>
       </c>
@@ -767,8 +1012,14 @@
         <v>8</v>
       </c>
       <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>10</v>
       </c>
@@ -782,8 +1033,14 @@
         <v>11</v>
       </c>
       <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F17" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>10</v>
       </c>
@@ -797,8 +1054,14 @@
         <v>13</v>
       </c>
       <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>10</v>
       </c>
@@ -812,8 +1075,14 @@
         <v>15</v>
       </c>
       <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>10</v>
       </c>
@@ -827,8 +1096,14 @@
         <v>12</v>
       </c>
       <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F20" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>10</v>
       </c>
@@ -842,8 +1117,14 @@
         <v>11</v>
       </c>
       <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F21" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>10</v>
       </c>
@@ -857,8 +1138,14 @@
         <v>13</v>
       </c>
       <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F22" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>10</v>
       </c>
@@ -872,8 +1159,14 @@
         <v>14</v>
       </c>
       <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>10</v>
       </c>
@@ -887,8 +1180,14 @@
         <v>12</v>
       </c>
       <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F24" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>10</v>
       </c>
@@ -902,8 +1201,14 @@
         <v>11</v>
       </c>
       <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F25" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>10</v>
       </c>
@@ -917,8 +1222,14 @@
         <v>15</v>
       </c>
       <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F26" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>10</v>
       </c>
@@ -932,8 +1243,14 @@
         <v>14</v>
       </c>
       <c r="E27" s="3"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F27" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>10</v>
       </c>
@@ -947,8 +1264,14 @@
         <v>12</v>
       </c>
       <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F28" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>10</v>
       </c>
@@ -962,8 +1285,14 @@
         <v>13</v>
       </c>
       <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F29" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>10</v>
       </c>
@@ -977,8 +1306,14 @@
         <v>15</v>
       </c>
       <c r="E30" s="3"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F30" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>10</v>
       </c>
@@ -992,8 +1327,14 @@
         <v>14</v>
       </c>
       <c r="E31" s="3"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F31" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <v>11</v>
       </c>
@@ -1007,8 +1348,14 @@
         <v>17</v>
       </c>
       <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F32" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>11</v>
       </c>
@@ -1022,8 +1369,14 @@
         <v>19</v>
       </c>
       <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F33" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>11</v>
       </c>
@@ -1037,8 +1390,14 @@
         <v>21</v>
       </c>
       <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F34" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>11</v>
       </c>
@@ -1052,8 +1411,14 @@
         <v>18</v>
       </c>
       <c r="E35" s="3"/>
-    </row>
-    <row r="36" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F35" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>11</v>
       </c>
@@ -1067,8 +1432,14 @@
         <v>17</v>
       </c>
       <c r="E36" s="3"/>
-    </row>
-    <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F36" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>11</v>
       </c>
@@ -1082,8 +1453,14 @@
         <v>19</v>
       </c>
       <c r="E37" s="3"/>
-    </row>
-    <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F37" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>11</v>
       </c>
@@ -1097,8 +1474,14 @@
         <v>20</v>
       </c>
       <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F38" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>11</v>
       </c>
@@ -1112,8 +1495,14 @@
         <v>18</v>
       </c>
       <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F39" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>11</v>
       </c>
@@ -1127,8 +1516,14 @@
         <v>17</v>
       </c>
       <c r="E40" s="3"/>
-    </row>
-    <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F40" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <v>11</v>
       </c>
@@ -1142,8 +1537,14 @@
         <v>21</v>
       </c>
       <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F41" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
         <v>11</v>
       </c>
@@ -1157,8 +1558,14 @@
         <v>20</v>
       </c>
       <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F42" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
         <v>11</v>
       </c>
@@ -1172,8 +1579,14 @@
         <v>18</v>
       </c>
       <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F43" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>11</v>
       </c>
@@ -1187,8 +1600,14 @@
         <v>19</v>
       </c>
       <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F44" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>11</v>
       </c>
@@ -1202,8 +1621,14 @@
         <v>21</v>
       </c>
       <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F45" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <v>11</v>
       </c>
@@ -1217,8 +1642,14 @@
         <v>20</v>
       </c>
       <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F46" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
         <v>12</v>
       </c>
@@ -1232,8 +1663,14 @@
         <v>23</v>
       </c>
       <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F47" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <v>12</v>
       </c>
@@ -1247,8 +1684,14 @@
         <v>25</v>
       </c>
       <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F48" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
         <v>12</v>
       </c>
@@ -1262,8 +1705,14 @@
         <v>27</v>
       </c>
       <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F49" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
         <v>12</v>
       </c>
@@ -1277,8 +1726,14 @@
         <v>24</v>
       </c>
       <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F50" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
         <v>12</v>
       </c>
@@ -1292,8 +1747,14 @@
         <v>23</v>
       </c>
       <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F51" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
         <v>12</v>
       </c>
@@ -1307,8 +1768,14 @@
         <v>25</v>
       </c>
       <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F52" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
         <v>12</v>
       </c>
@@ -1322,8 +1789,14 @@
         <v>26</v>
       </c>
       <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F53" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
         <v>12</v>
       </c>
@@ -1337,8 +1810,14 @@
         <v>24</v>
       </c>
       <c r="E54" s="3"/>
-    </row>
-    <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F54" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
         <v>12</v>
       </c>
@@ -1352,8 +1831,14 @@
         <v>23</v>
       </c>
       <c r="E55" s="3"/>
-    </row>
-    <row r="56" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F55" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
         <v>12</v>
       </c>
@@ -1367,8 +1852,14 @@
         <v>27</v>
       </c>
       <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F56" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
         <v>12</v>
       </c>
@@ -1382,8 +1873,14 @@
         <v>26</v>
       </c>
       <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F57" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
         <v>12</v>
       </c>
@@ -1397,8 +1894,14 @@
         <v>24</v>
       </c>
       <c r="E58" s="3"/>
-    </row>
-    <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F58" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
         <v>12</v>
       </c>
@@ -1412,8 +1915,14 @@
         <v>25</v>
       </c>
       <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F59" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
         <v>12</v>
       </c>
@@ -1427,8 +1936,14 @@
         <v>27</v>
       </c>
       <c r="E60" s="3"/>
-    </row>
-    <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="F60" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
         <v>12</v>
       </c>
@@ -1442,6 +1957,12 @@
         <v>26</v>
       </c>
       <c r="E61" s="3"/>
+      <c r="F61" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
